--- a/backend/data/financials_by_company/1636.HK.xlsx
+++ b/backend/data/financials_by_company/1636.HK.xlsx
@@ -667,592 +667,592 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-119255.59454</v>
+        <v>-1526250</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001648</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-191994000</v>
+        <v>225879000</v>
       </c>
       <c r="E2" t="n">
-        <v>-72366000</v>
+        <v>-6105000</v>
       </c>
       <c r="F2" t="n">
-        <v>-72366000</v>
+        <v>-6105000</v>
       </c>
       <c r="G2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="H2" t="n">
-        <v>35124000</v>
+        <v>53053000</v>
       </c>
       <c r="I2" t="n">
-        <v>498765000</v>
+        <v>7567848000</v>
       </c>
       <c r="J2" t="n">
-        <v>-264360000</v>
+        <v>219774000</v>
       </c>
       <c r="K2" t="n">
-        <v>-299484000</v>
+        <v>166721000</v>
       </c>
       <c r="L2" t="n">
-        <v>-354027000</v>
+        <v>-208849000</v>
       </c>
       <c r="M2" t="n">
-        <v>354055000</v>
+        <v>220860000</v>
       </c>
       <c r="N2" t="n">
-        <v>28000</v>
+        <v>12634000</v>
       </c>
       <c r="O2" t="n">
-        <v>-580215255.59454</v>
+        <v>-90898250</v>
       </c>
       <c r="P2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="Q2" t="n">
-        <v>681076000</v>
+        <v>7580666000</v>
       </c>
       <c r="R2" t="n">
-        <v>448155726</v>
+        <v>319007541</v>
       </c>
       <c r="S2" t="n">
-        <v>448155726</v>
+        <v>319007541</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5</v>
+        <v>-0.3</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5</v>
+        <v>-0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="W2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-652462000</v>
+        <v>-95477000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1077000</v>
+        <v>41338000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-653539000</v>
+        <v>-54139000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7969000</v>
+        <v>31448000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-72366000</v>
+        <v>-5873000</v>
       </c>
       <c r="AF2" t="n">
-        <v>52000</v>
+        <v>-34985000</v>
       </c>
       <c r="AG2" t="n">
-        <v>72314000</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>5873000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1452000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-354027000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-208849000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>623000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>354055000</v>
+        <v>220860000</v>
       </c>
       <c r="AM2" t="n">
-        <v>28000</v>
+        <v>12634000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-218094000</v>
+        <v>130024000</v>
       </c>
       <c r="AO2" t="n">
-        <v>182311000</v>
+        <v>12818000</v>
       </c>
       <c r="AP2" t="n">
-        <v>108785000</v>
+        <v>-10586000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>104590000</v>
+        <v>150137000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1600000</v>
+        <v>18182000</v>
       </c>
       <c r="AS2" t="n">
-        <v>102990000</v>
+        <v>131955000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-35783000</v>
+        <v>142842000</v>
       </c>
       <c r="AU2" t="n">
-        <v>498765000</v>
+        <v>7567848000</v>
       </c>
       <c r="AV2" t="n">
-        <v>462982000</v>
+        <v>7710690000</v>
       </c>
       <c r="AW2" t="n">
-        <v>462982000</v>
+        <v>7710690000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-52014000</v>
+        <v>-489703500</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-281328000</v>
+        <v>-2523875000</v>
       </c>
       <c r="E3" t="n">
-        <v>-208056000</v>
+        <v>-1958814000</v>
       </c>
       <c r="F3" t="n">
-        <v>-208056000</v>
+        <v>-1958814000</v>
       </c>
       <c r="G3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="H3" t="n">
-        <v>42366000</v>
+        <v>51111000</v>
       </c>
       <c r="I3" t="n">
-        <v>949599000</v>
+        <v>2679759000</v>
       </c>
       <c r="J3" t="n">
-        <v>-489384000</v>
+        <v>-4482689000</v>
       </c>
       <c r="K3" t="n">
-        <v>-531750000</v>
+        <v>-4533800000</v>
       </c>
       <c r="L3" t="n">
-        <v>-270575000</v>
+        <v>-206761000</v>
       </c>
       <c r="M3" t="n">
-        <v>274017000</v>
+        <v>227425000</v>
       </c>
       <c r="N3" t="n">
-        <v>7085000</v>
+        <v>27449000</v>
       </c>
       <c r="O3" t="n">
-        <v>-649738000</v>
+        <v>-3294041500</v>
       </c>
       <c r="P3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1147301000</v>
+        <v>4999650000</v>
       </c>
       <c r="R3" t="n">
-        <v>448155726</v>
+        <v>432983395</v>
       </c>
       <c r="S3" t="n">
-        <v>448155726</v>
+        <v>432983395</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.8</v>
+        <v>-11</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.8</v>
+        <v>-11</v>
       </c>
       <c r="V3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="W3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-805780000</v>
+        <v>-4763152000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13000</v>
+        <v>1927000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-805767000</v>
+        <v>-4761225000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1223000</v>
+        <v>4097000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-208056000</v>
+        <v>-1958814000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-119000</v>
+        <v>5567000</v>
       </c>
       <c r="AG3" t="n">
-        <v>208106000</v>
+        <v>1950034000</v>
       </c>
       <c r="AH3" t="n">
-        <v>69000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>3213000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>-270575000</v>
+        <v>-206761000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3643000</v>
+        <v>6785000</v>
       </c>
       <c r="AL3" t="n">
-        <v>274017000</v>
+        <v>227425000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7085000</v>
+        <v>27449000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-327394000</v>
+        <v>-2609616000</v>
       </c>
       <c r="AO3" t="n">
-        <v>197702000</v>
+        <v>2319891000</v>
       </c>
       <c r="AP3" t="n">
-        <v>117559000</v>
+        <v>2194887000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>117858000</v>
+        <v>203154000</v>
       </c>
       <c r="AR3" t="n">
-        <v>7197000</v>
+        <v>7910000</v>
       </c>
       <c r="AS3" t="n">
-        <v>110661000</v>
+        <v>195244000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-129692000</v>
+        <v>-289725000</v>
       </c>
       <c r="AU3" t="n">
-        <v>949599000</v>
+        <v>2679759000</v>
       </c>
       <c r="AV3" t="n">
-        <v>819907000</v>
+        <v>2390034000</v>
       </c>
       <c r="AW3" t="n">
-        <v>819907000</v>
+        <v>2390034000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-489703500</v>
+        <v>-52014000</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-2523875000</v>
+        <v>-281328000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1958814000</v>
+        <v>-208056000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1958814000</v>
+        <v>-208056000</v>
       </c>
       <c r="G4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="H4" t="n">
-        <v>51111000</v>
+        <v>42366000</v>
       </c>
       <c r="I4" t="n">
-        <v>2679759000</v>
+        <v>949599000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4482689000</v>
+        <v>-489384000</v>
       </c>
       <c r="K4" t="n">
-        <v>-4533800000</v>
+        <v>-531750000</v>
       </c>
       <c r="L4" t="n">
-        <v>-206761000</v>
+        <v>-270575000</v>
       </c>
       <c r="M4" t="n">
-        <v>227425000</v>
+        <v>274017000</v>
       </c>
       <c r="N4" t="n">
-        <v>27449000</v>
+        <v>7085000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3294041500</v>
+        <v>-649738000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4999650000</v>
+        <v>1147301000</v>
       </c>
       <c r="R4" t="n">
-        <v>432983395</v>
+        <v>448155726</v>
       </c>
       <c r="S4" t="n">
-        <v>432983395</v>
+        <v>448155726</v>
       </c>
       <c r="T4" t="n">
-        <v>-11</v>
+        <v>-1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>-11</v>
+        <v>-1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="W4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4763152000</v>
+        <v>-805780000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1927000</v>
+        <v>13000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4761225000</v>
+        <v>-805767000</v>
       </c>
       <c r="AD4" t="n">
-        <v>4097000</v>
+        <v>1223000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1958814000</v>
+        <v>-208056000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5567000</v>
+        <v>-119000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1950034000</v>
+        <v>208106000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3213000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>69000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-206761000</v>
+        <v>-270575000</v>
       </c>
       <c r="AK4" t="n">
-        <v>6785000</v>
+        <v>3643000</v>
       </c>
       <c r="AL4" t="n">
-        <v>227425000</v>
+        <v>274017000</v>
       </c>
       <c r="AM4" t="n">
-        <v>27449000</v>
+        <v>7085000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2609616000</v>
+        <v>-327394000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2319891000</v>
+        <v>197702000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2194887000</v>
+        <v>117559000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>203154000</v>
+        <v>117858000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7910000</v>
+        <v>7197000</v>
       </c>
       <c r="AS4" t="n">
-        <v>195244000</v>
+        <v>110661000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-289725000</v>
+        <v>-129692000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2679759000</v>
+        <v>949599000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2390034000</v>
+        <v>819907000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2390034000</v>
+        <v>819907000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1526250</v>
+        <v>-119255.59454</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.001648</v>
       </c>
       <c r="D5" t="n">
-        <v>225879000</v>
+        <v>-191994000</v>
       </c>
       <c r="E5" t="n">
-        <v>-6105000</v>
+        <v>-72366000</v>
       </c>
       <c r="F5" t="n">
-        <v>-6105000</v>
+        <v>-72366000</v>
       </c>
       <c r="G5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="H5" t="n">
-        <v>53053000</v>
+        <v>35124000</v>
       </c>
       <c r="I5" t="n">
-        <v>7567848000</v>
+        <v>498765000</v>
       </c>
       <c r="J5" t="n">
-        <v>219774000</v>
+        <v>-264360000</v>
       </c>
       <c r="K5" t="n">
-        <v>166721000</v>
+        <v>-299484000</v>
       </c>
       <c r="L5" t="n">
-        <v>-208849000</v>
+        <v>-354027000</v>
       </c>
       <c r="M5" t="n">
-        <v>220860000</v>
+        <v>354055000</v>
       </c>
       <c r="N5" t="n">
-        <v>12634000</v>
+        <v>28000</v>
       </c>
       <c r="O5" t="n">
-        <v>-90898250</v>
+        <v>-580215255.59454</v>
       </c>
       <c r="P5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="Q5" t="n">
-        <v>7580666000</v>
+        <v>681076000</v>
       </c>
       <c r="R5" t="n">
-        <v>319007541</v>
+        <v>448155726</v>
       </c>
       <c r="S5" t="n">
-        <v>319007541</v>
+        <v>448155726</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="W5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-95477000</v>
+        <v>-652462000</v>
       </c>
       <c r="AB5" t="n">
-        <v>41338000</v>
+        <v>-1077000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-54139000</v>
+        <v>-653539000</v>
       </c>
       <c r="AD5" t="n">
-        <v>31448000</v>
+        <v>-7969000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5873000</v>
+        <v>-72366000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-34985000</v>
+        <v>52000</v>
       </c>
       <c r="AG5" t="n">
+        <v>72314000</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="n">
-        <v>5873000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1452000</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-208849000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>623000</v>
-      </c>
+        <v>-354027000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>220860000</v>
+        <v>354055000</v>
       </c>
       <c r="AM5" t="n">
-        <v>12634000</v>
+        <v>28000</v>
       </c>
       <c r="AN5" t="n">
-        <v>130024000</v>
+        <v>-218094000</v>
       </c>
       <c r="AO5" t="n">
-        <v>12818000</v>
+        <v>182311000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-10586000</v>
+        <v>108785000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>150137000</v>
+        <v>104590000</v>
       </c>
       <c r="AR5" t="n">
-        <v>18182000</v>
+        <v>1600000</v>
       </c>
       <c r="AS5" t="n">
-        <v>131955000</v>
+        <v>102990000</v>
       </c>
       <c r="AT5" t="n">
-        <v>142842000</v>
+        <v>-35783000</v>
       </c>
       <c r="AU5" t="n">
-        <v>7567848000</v>
+        <v>498765000</v>
       </c>
       <c r="AV5" t="n">
-        <v>7710690000</v>
+        <v>462982000</v>
       </c>
       <c r="AW5" t="n">
-        <v>7710690000</v>
+        <v>462982000</v>
       </c>
     </row>
   </sheetData>
@@ -1603,194 +1603,210 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>448155726</v>
+        <v>345602006</v>
       </c>
       <c r="C2" t="n">
-        <v>448155726</v>
+        <v>345602006</v>
       </c>
       <c r="D2" t="n">
-        <v>1662761000</v>
+        <v>1780853000</v>
       </c>
       <c r="E2" t="n">
-        <v>1666374000</v>
+        <v>1799964000</v>
       </c>
       <c r="F2" t="n">
-        <v>-4257349000</v>
+        <v>1602934000</v>
       </c>
       <c r="G2" t="n">
-        <v>-2495129000</v>
+        <v>3502203000</v>
       </c>
       <c r="H2" t="n">
-        <v>-4711009000</v>
+        <v>1026442000</v>
       </c>
       <c r="I2" t="n">
-        <v>-4257349000</v>
+        <v>1602934000</v>
       </c>
       <c r="J2" t="n">
+        <v>7158000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1709397000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1709397000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1709397000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1709397000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14938000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-752651000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1901321000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>280461000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>280461000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5024602000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10706000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6558000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>936000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3212000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3212000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5013896000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>121383000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1796752000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3946000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1792806000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2776800000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>331866000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1101249000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1343685000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6733999000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>693661000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19756000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>19756000</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>-4161503000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-4161503000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-4161503000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-4161503000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>22849000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-6973573000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2204701000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>363611000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>363611000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5244623000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>5244623000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>1666374000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1666374000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3162947000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1303861000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1069798000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>789288000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1083120000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>549506000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>46484000</v>
+        <v>48001000</v>
       </c>
       <c r="AO2" t="n">
-        <v>46484000</v>
+        <v>48001000</v>
       </c>
       <c r="AP2" t="n">
-        <v>95846000</v>
+        <v>106463000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>95846000</v>
+        <v>106463000</v>
       </c>
       <c r="AR2" t="n">
-        <v>407176000</v>
+        <v>539197000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-451698000</v>
+        <v>-394467000</v>
       </c>
       <c r="AT2" t="n">
-        <v>858874000</v>
+        <v>933664000</v>
       </c>
       <c r="AU2" t="n">
-        <v>157424000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>167398000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>512702000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>302885000</v>
+        <v>361922000</v>
       </c>
       <c r="AX2" t="n">
-        <v>398565000</v>
+        <v>404344000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>533614000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>6040338000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="n">
-        <v>32262000</v>
+        <v>873359000</v>
       </c>
       <c r="BC2" t="n">
-        <v>211840000</v>
+        <v>2214484000</v>
       </c>
       <c r="BD2" t="n">
-        <v>39208000</v>
+        <v>189455000</v>
       </c>
       <c r="BE2" t="n">
-        <v>136000</v>
+        <v>41896000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1639000</v>
+        <v>2939000</v>
       </c>
       <c r="BG2" t="n">
-        <v>37433000</v>
+        <v>144620000</v>
       </c>
       <c r="BH2" t="n">
-        <v>70797000</v>
+        <v>255339000</v>
       </c>
       <c r="BI2" t="n">
-        <v>162640000</v>
+        <v>184283000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13254000</v>
+        <v>2311465000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-394554000</v>
+        <v>-234789000</v>
       </c>
       <c r="BL2" t="n">
-        <v>407808000</v>
+        <v>2546254000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3613000</v>
+        <v>11953000</v>
       </c>
       <c r="BN2" t="n">
-        <v>3613000</v>
+        <v>11953000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3613000</v>
+        <v>11953000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>448155726</v>
@@ -1799,43 +1815,43 @@
         <v>448155726</v>
       </c>
       <c r="D3" t="n">
-        <v>1633595000</v>
+        <v>1591210000</v>
       </c>
       <c r="E3" t="n">
-        <v>1652301000</v>
+        <v>1595831000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3606706000</v>
+        <v>-2804978000</v>
       </c>
       <c r="G3" t="n">
-        <v>-1855290000</v>
+        <v>-1108399000</v>
       </c>
       <c r="H3" t="n">
-        <v>-4090155000</v>
+        <v>-3318727000</v>
       </c>
       <c r="I3" t="n">
-        <v>-3606706000</v>
+        <v>-2804978000</v>
       </c>
       <c r="J3" t="n">
-        <v>379000</v>
+        <v>2230000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3507212000</v>
+        <v>-2702000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-3507212000</v>
+        <v>-2702000000</v>
       </c>
       <c r="M3" t="n">
-        <v>-3507212000</v>
+        <v>-2702000000</v>
       </c>
       <c r="N3" t="n">
-        <v>-3507212000</v>
+        <v>-2702000000</v>
       </c>
       <c r="O3" t="n">
-        <v>21875000</v>
+        <v>19844000</v>
       </c>
       <c r="P3" t="n">
-        <v>-6321181000</v>
+        <v>-5515773000</v>
       </c>
       <c r="Q3" t="n">
         <v>2204701000</v>
@@ -1847,141 +1863,145 @@
         <v>363611000</v>
       </c>
       <c r="T3" t="n">
-        <v>4889531000</v>
+        <v>5100071000</v>
       </c>
       <c r="U3" t="n">
-        <v>1796000</v>
+        <v>2846000</v>
       </c>
       <c r="V3" t="n">
-        <v>644000</v>
+        <v>1322000</v>
       </c>
       <c r="W3" t="n">
         <v>1152000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>372000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>372000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4887735000</v>
+        <v>5097225000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1652301000</v>
+        <v>1595459000</v>
       </c>
       <c r="AC3" t="n">
-        <v>379000</v>
+        <v>1858000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1651922000</v>
+        <v>1593601000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2804510000</v>
+        <v>3233144000</v>
       </c>
       <c r="AF3" t="n">
-        <v>938481000</v>
+        <v>597820000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1076320000</v>
+        <v>1021688000</v>
       </c>
       <c r="AH3" t="n">
-        <v>789709000</v>
+        <v>1613636000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1382319000</v>
+        <v>2398071000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>584739000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>619573000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>19756000</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>46807000</v>
+        <v>47106000</v>
       </c>
       <c r="AO3" t="n">
-        <v>46807000</v>
+        <v>47106000</v>
       </c>
       <c r="AP3" t="n">
-        <v>99494000</v>
+        <v>102978000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>99494000</v>
+        <v>102978000</v>
       </c>
       <c r="AR3" t="n">
-        <v>438438000</v>
+        <v>469489000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-421241000</v>
+        <v>-410644000</v>
       </c>
       <c r="AT3" t="n">
-        <v>859679000</v>
+        <v>880133000</v>
       </c>
       <c r="AU3" t="n">
-        <v>157307000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>159596000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>448216000</v>
+      </c>
       <c r="AW3" t="n">
-        <v>303471000</v>
+        <v>319707000</v>
       </c>
       <c r="AX3" t="n">
-        <v>398901000</v>
+        <v>400830000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>797580000</v>
+        <v>1778498000</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>32262000</v>
+        <v>703928000</v>
       </c>
       <c r="BC3" t="n">
-        <v>292240000</v>
+        <v>511937000</v>
       </c>
       <c r="BD3" t="n">
-        <v>64536000</v>
+        <v>100946000</v>
       </c>
       <c r="BE3" t="n">
-        <v>11876000</v>
+        <v>50510000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1677000</v>
+        <v>2539000</v>
       </c>
       <c r="BG3" t="n">
-        <v>50983000</v>
+        <v>47897000</v>
       </c>
       <c r="BH3" t="n">
-        <v>126030000</v>
+        <v>116377000</v>
       </c>
       <c r="BI3" t="n">
-        <v>162298000</v>
+        <v>178393000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>101887000</v>
+        <v>164526000</v>
       </c>
       <c r="BK3" t="n">
-        <v>-317130000</v>
+        <v>-275019000</v>
       </c>
       <c r="BL3" t="n">
-        <v>419017000</v>
+        <v>439545000</v>
       </c>
       <c r="BM3" t="n">
-        <v>18327000</v>
+        <v>2391000</v>
       </c>
       <c r="BN3" t="n">
-        <v>18327000</v>
+        <v>2391000</v>
       </c>
       <c r="BO3" t="n">
-        <v>18327000</v>
+        <v>2391000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>448155726</v>
@@ -1990,43 +2010,43 @@
         <v>448155726</v>
       </c>
       <c r="D4" t="n">
-        <v>1591210000</v>
+        <v>1633595000</v>
       </c>
       <c r="E4" t="n">
-        <v>1595831000</v>
+        <v>1652301000</v>
       </c>
       <c r="F4" t="n">
-        <v>-2804978000</v>
+        <v>-3606706000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1108399000</v>
+        <v>-1855290000</v>
       </c>
       <c r="H4" t="n">
-        <v>-3318727000</v>
+        <v>-4090155000</v>
       </c>
       <c r="I4" t="n">
-        <v>-2804978000</v>
+        <v>-3606706000</v>
       </c>
       <c r="J4" t="n">
-        <v>2230000</v>
+        <v>379000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2702000000</v>
+        <v>-3507212000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2702000000</v>
+        <v>-3507212000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2702000000</v>
+        <v>-3507212000</v>
       </c>
       <c r="N4" t="n">
-        <v>-2702000000</v>
+        <v>-3507212000</v>
       </c>
       <c r="O4" t="n">
-        <v>19844000</v>
+        <v>21875000</v>
       </c>
       <c r="P4" t="n">
-        <v>-5515773000</v>
+        <v>-6321181000</v>
       </c>
       <c r="Q4" t="n">
         <v>2204701000</v>
@@ -2038,343 +2058,323 @@
         <v>363611000</v>
       </c>
       <c r="T4" t="n">
-        <v>5100071000</v>
+        <v>4889531000</v>
       </c>
       <c r="U4" t="n">
-        <v>2846000</v>
+        <v>1796000</v>
       </c>
       <c r="V4" t="n">
-        <v>1322000</v>
+        <v>644000</v>
       </c>
       <c r="W4" t="n">
         <v>1152000</v>
       </c>
       <c r="X4" t="n">
-        <v>372000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>372000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5097225000</v>
+        <v>4887735000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>1595459000</v>
+        <v>1652301000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1858000</v>
+        <v>379000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1593601000</v>
+        <v>1651922000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3233144000</v>
+        <v>2804510000</v>
       </c>
       <c r="AF4" t="n">
-        <v>597820000</v>
+        <v>938481000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1021688000</v>
+        <v>1076320000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1613636000</v>
+        <v>789709000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2398071000</v>
+        <v>1382319000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>619573000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>19756000</v>
-      </c>
+        <v>584739000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>47106000</v>
+        <v>46807000</v>
       </c>
       <c r="AO4" t="n">
-        <v>47106000</v>
+        <v>46807000</v>
       </c>
       <c r="AP4" t="n">
-        <v>102978000</v>
+        <v>99494000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>102978000</v>
+        <v>99494000</v>
       </c>
       <c r="AR4" t="n">
-        <v>469489000</v>
+        <v>438438000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-410644000</v>
+        <v>-421241000</v>
       </c>
       <c r="AT4" t="n">
-        <v>880133000</v>
+        <v>859679000</v>
       </c>
       <c r="AU4" t="n">
-        <v>159596000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>448216000</v>
-      </c>
+        <v>157307000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>319707000</v>
+        <v>303471000</v>
       </c>
       <c r="AX4" t="n">
-        <v>400830000</v>
+        <v>398901000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1778498000</v>
+        <v>797580000</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>703928000</v>
+        <v>32262000</v>
       </c>
       <c r="BC4" t="n">
-        <v>511937000</v>
+        <v>292240000</v>
       </c>
       <c r="BD4" t="n">
-        <v>100946000</v>
+        <v>64536000</v>
       </c>
       <c r="BE4" t="n">
-        <v>50510000</v>
+        <v>11876000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2539000</v>
+        <v>1677000</v>
       </c>
       <c r="BG4" t="n">
-        <v>47897000</v>
+        <v>50983000</v>
       </c>
       <c r="BH4" t="n">
-        <v>116377000</v>
+        <v>126030000</v>
       </c>
       <c r="BI4" t="n">
-        <v>178393000</v>
+        <v>162298000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>164526000</v>
+        <v>101887000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-275019000</v>
+        <v>-317130000</v>
       </c>
       <c r="BL4" t="n">
-        <v>439545000</v>
+        <v>419017000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2391000</v>
+        <v>18327000</v>
       </c>
       <c r="BN4" t="n">
-        <v>2391000</v>
+        <v>18327000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2391000</v>
+        <v>18327000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>345602006</v>
+        <v>448155726</v>
       </c>
       <c r="C5" t="n">
-        <v>345602006</v>
+        <v>448155726</v>
       </c>
       <c r="D5" t="n">
-        <v>1780853000</v>
+        <v>1662761000</v>
       </c>
       <c r="E5" t="n">
-        <v>1799964000</v>
+        <v>1666374000</v>
       </c>
       <c r="F5" t="n">
-        <v>1602934000</v>
+        <v>-4257349000</v>
       </c>
       <c r="G5" t="n">
-        <v>3502203000</v>
+        <v>-2495129000</v>
       </c>
       <c r="H5" t="n">
-        <v>1026442000</v>
+        <v>-4711009000</v>
       </c>
       <c r="I5" t="n">
-        <v>1602934000</v>
+        <v>-4257349000</v>
       </c>
       <c r="J5" t="n">
-        <v>7158000</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1709397000</v>
+        <v>-4161503000</v>
       </c>
       <c r="L5" t="n">
-        <v>1709397000</v>
+        <v>-4161503000</v>
       </c>
       <c r="M5" t="n">
-        <v>1709397000</v>
+        <v>-4161503000</v>
       </c>
       <c r="N5" t="n">
-        <v>1709397000</v>
+        <v>-4161503000</v>
       </c>
       <c r="O5" t="n">
-        <v>14938000</v>
+        <v>22849000</v>
       </c>
       <c r="P5" t="n">
-        <v>-752651000</v>
+        <v>-6973573000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1901321000</v>
+        <v>2204701000</v>
       </c>
       <c r="R5" t="n">
-        <v>280461000</v>
+        <v>363611000</v>
       </c>
       <c r="S5" t="n">
-        <v>280461000</v>
+        <v>363611000</v>
       </c>
       <c r="T5" t="n">
-        <v>5024602000</v>
+        <v>5244623000</v>
       </c>
       <c r="U5" t="n">
-        <v>10706000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6558000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>936000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3212000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3212000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>5013896000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>121383000</v>
-      </c>
+        <v>5244623000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>1796752000</v>
+        <v>1666374000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3946000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1792806000</v>
+        <v>1666374000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2776800000</v>
+        <v>3162947000</v>
       </c>
       <c r="AF5" t="n">
-        <v>331866000</v>
+        <v>1303861000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1101249000</v>
+        <v>1069798000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1343685000</v>
+        <v>789288000</v>
       </c>
       <c r="AI5" t="n">
-        <v>6733999000</v>
+        <v>1083120000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>693661000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19756000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>19756000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>549506000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>48001000</v>
+        <v>46484000</v>
       </c>
       <c r="AO5" t="n">
-        <v>48001000</v>
+        <v>46484000</v>
       </c>
       <c r="AP5" t="n">
-        <v>106463000</v>
+        <v>95846000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>106463000</v>
+        <v>95846000</v>
       </c>
       <c r="AR5" t="n">
-        <v>539197000</v>
+        <v>407176000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-394467000</v>
+        <v>-451698000</v>
       </c>
       <c r="AT5" t="n">
-        <v>933664000</v>
+        <v>858874000</v>
       </c>
       <c r="AU5" t="n">
-        <v>167398000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>512702000</v>
-      </c>
+        <v>157424000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>361922000</v>
+        <v>302885000</v>
       </c>
       <c r="AX5" t="n">
-        <v>404344000</v>
+        <v>398565000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6040338000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
+        <v>533614000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>873359000</v>
+        <v>32262000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2214484000</v>
+        <v>211840000</v>
       </c>
       <c r="BD5" t="n">
-        <v>189455000</v>
+        <v>39208000</v>
       </c>
       <c r="BE5" t="n">
-        <v>41896000</v>
+        <v>136000</v>
       </c>
       <c r="BF5" t="n">
-        <v>2939000</v>
+        <v>1639000</v>
       </c>
       <c r="BG5" t="n">
-        <v>144620000</v>
+        <v>37433000</v>
       </c>
       <c r="BH5" t="n">
-        <v>255339000</v>
+        <v>70797000</v>
       </c>
       <c r="BI5" t="n">
-        <v>184283000</v>
+        <v>162640000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2311465000</v>
+        <v>13254000</v>
       </c>
       <c r="BK5" t="n">
-        <v>-234789000</v>
+        <v>-394554000</v>
       </c>
       <c r="BL5" t="n">
-        <v>2546254000</v>
+        <v>407808000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11953000</v>
+        <v>3613000</v>
       </c>
       <c r="BN5" t="n">
-        <v>11953000</v>
+        <v>3613000</v>
       </c>
       <c r="BO5" t="n">
-        <v>11953000</v>
+        <v>3613000</v>
       </c>
     </row>
   </sheetData>
@@ -2590,462 +2590,462 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-18035000</v>
+        <v>114201000</v>
       </c>
       <c r="C2" t="n">
+        <v>-316428000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>539253000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1867000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11953000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47321000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>975000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-36343000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>228049000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>44815000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-36141000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>222825000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>222825000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-316428000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>539253000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>222825000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-316428000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>539253000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-380460000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-347457000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>18705000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1867000</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-380000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3613000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18327000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-28000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-14686000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3002000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-4034000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-4585000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="Y2" t="n">
+        <v>-1867000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>116068000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-3721000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-164804000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>273259000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-280062000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>127321000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-285322000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>175316000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>273000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>103558000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>53053000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>53053000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>232000</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>-33000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>28000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>31000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>411000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-380000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-17655000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>165000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>51006000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4098000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18567000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25328000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11209000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>354027000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1044000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>121829000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>35124000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>35124000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>52000</v>
-      </c>
       <c r="AN2" t="n">
-        <v>-653539000</v>
+        <v>-54139000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-69811000</v>
+        <v>-212381000</v>
       </c>
       <c r="C3" t="n">
-        <v>-268000</v>
+        <v>-25824000</v>
       </c>
       <c r="D3" t="n">
-        <v>80600000</v>
+        <v>46023000</v>
       </c>
       <c r="E3" t="n">
-        <v>-498000</v>
+        <v>-91000</v>
       </c>
       <c r="F3" t="n">
-        <v>18327000</v>
+        <v>2391000</v>
       </c>
       <c r="G3" t="n">
-        <v>2391000</v>
+        <v>11953000</v>
       </c>
       <c r="H3" t="n">
-        <v>-17000</v>
+        <v>-82000</v>
       </c>
       <c r="I3" t="n">
-        <v>15953000</v>
+        <v>-9480000</v>
       </c>
       <c r="J3" t="n">
-        <v>70907000</v>
+        <v>4519000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3764000</v>
+        <v>-1000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-3797000</v>
+        <v>-11208000</v>
       </c>
       <c r="M3" t="n">
-        <v>80332000</v>
+        <v>20199000</v>
       </c>
       <c r="N3" t="n">
-        <v>80332000</v>
+        <v>20199000</v>
       </c>
       <c r="O3" t="n">
-        <v>-268000</v>
+        <v>-25824000</v>
       </c>
       <c r="P3" t="n">
-        <v>80600000</v>
+        <v>46023000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>14359000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>198291000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>169431000</v>
+      </c>
       <c r="V3" t="n">
-        <v>17183000</v>
+        <v>25577000</v>
       </c>
       <c r="W3" t="n">
-        <v>-159000</v>
+        <v>2749000</v>
       </c>
       <c r="X3" t="n">
-        <v>339000</v>
+        <v>2840000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-498000</v>
+        <v>-91000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-69313000</v>
+        <v>-212290000</v>
       </c>
       <c r="AA3" t="n">
-        <v>230000</v>
+        <v>-1617000</v>
       </c>
       <c r="AB3" t="n">
-        <v>68046000</v>
+        <v>35634000</v>
       </c>
       <c r="AC3" t="n">
-        <v>110476000</v>
+        <v>193952000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-24563000</v>
+        <v>-29296000</v>
       </c>
       <c r="AE3" t="n">
-        <v>33909000</v>
+        <v>18680000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-51776000</v>
+        <v>-147702000</v>
       </c>
       <c r="AG3" t="n">
-        <v>270575000</v>
+        <v>205829000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2403000</v>
+        <v>4939000</v>
       </c>
       <c r="AI3" t="n">
-        <v>144479000</v>
+        <v>2292502000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42366000</v>
+        <v>51111000</v>
       </c>
       <c r="AK3" t="n">
-        <v>42366000</v>
+        <v>51111000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-119000</v>
+        <v>6499000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-805767000</v>
+        <v>-4761225000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-212381000</v>
+        <v>-69811000</v>
       </c>
       <c r="C4" t="n">
-        <v>-25824000</v>
+        <v>-268000</v>
       </c>
       <c r="D4" t="n">
-        <v>46023000</v>
+        <v>80600000</v>
       </c>
       <c r="E4" t="n">
-        <v>-91000</v>
+        <v>-498000</v>
       </c>
       <c r="F4" t="n">
+        <v>18327000</v>
+      </c>
+      <c r="G4" t="n">
         <v>2391000</v>
       </c>
-      <c r="G4" t="n">
-        <v>11953000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-82000</v>
+        <v>-17000</v>
       </c>
       <c r="I4" t="n">
-        <v>-9480000</v>
+        <v>15953000</v>
       </c>
       <c r="J4" t="n">
-        <v>4519000</v>
+        <v>70907000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1000000</v>
+        <v>-3764000</v>
       </c>
       <c r="L4" t="n">
-        <v>-11208000</v>
+        <v>-3797000</v>
       </c>
       <c r="M4" t="n">
-        <v>20199000</v>
+        <v>80332000</v>
       </c>
       <c r="N4" t="n">
-        <v>20199000</v>
+        <v>80332000</v>
       </c>
       <c r="O4" t="n">
-        <v>-25824000</v>
+        <v>-268000</v>
       </c>
       <c r="P4" t="n">
-        <v>46023000</v>
+        <v>80600000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>198291000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>169431000</v>
-      </c>
+        <v>14359000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>25577000</v>
+        <v>17183000</v>
       </c>
       <c r="W4" t="n">
-        <v>2749000</v>
+        <v>-159000</v>
       </c>
       <c r="X4" t="n">
-        <v>2840000</v>
+        <v>339000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-91000</v>
+        <v>-498000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-212290000</v>
+        <v>-69313000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1617000</v>
+        <v>230000</v>
       </c>
       <c r="AB4" t="n">
-        <v>35634000</v>
+        <v>68046000</v>
       </c>
       <c r="AC4" t="n">
-        <v>193952000</v>
+        <v>110476000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-29296000</v>
+        <v>-24563000</v>
       </c>
       <c r="AE4" t="n">
-        <v>18680000</v>
+        <v>33909000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-147702000</v>
+        <v>-51776000</v>
       </c>
       <c r="AG4" t="n">
-        <v>205829000</v>
+        <v>270575000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4939000</v>
+        <v>2403000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2292502000</v>
+        <v>144479000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>51111000</v>
+        <v>42366000</v>
       </c>
       <c r="AK4" t="n">
-        <v>51111000</v>
+        <v>42366000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>6499000</v>
+        <v>-119000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-4761225000</v>
+        <v>-805767000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>114201000</v>
+        <v>-18035000</v>
       </c>
       <c r="C5" t="n">
-        <v>-316428000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>539253000</v>
+        <v>12000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1867000</v>
+        <v>-380000</v>
       </c>
       <c r="F5" t="n">
-        <v>11953000</v>
+        <v>3613000</v>
       </c>
       <c r="G5" t="n">
-        <v>47321000</v>
+        <v>18327000</v>
       </c>
       <c r="H5" t="n">
-        <v>975000</v>
+        <v>-28000</v>
       </c>
       <c r="I5" t="n">
-        <v>-36343000</v>
+        <v>-14686000</v>
       </c>
       <c r="J5" t="n">
-        <v>228049000</v>
+        <v>3002000</v>
       </c>
       <c r="K5" t="n">
-        <v>44815000</v>
+        <v>-4034000</v>
       </c>
       <c r="L5" t="n">
-        <v>-36141000</v>
+        <v>-4585000</v>
       </c>
       <c r="M5" t="n">
-        <v>222825000</v>
+        <v>12000000</v>
       </c>
       <c r="N5" t="n">
-        <v>222825000</v>
+        <v>12000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-316428000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>539253000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>222825000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-316428000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>539253000</v>
-      </c>
+        <v>12000000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-380460000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-347457000</v>
-      </c>
+        <v>-33000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>18705000</v>
+        <v>28000</v>
       </c>
       <c r="W5" t="n">
-        <v>-1867000</v>
+        <v>31000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>411000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1867000</v>
+        <v>-380000</v>
       </c>
       <c r="Z5" t="n">
-        <v>116068000</v>
+        <v>-17655000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3721000</v>
+        <v>165000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-164804000</v>
+        <v>51006000</v>
       </c>
       <c r="AC5" t="n">
-        <v>273259000</v>
+        <v>-4098000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-280062000</v>
+        <v>18567000</v>
       </c>
       <c r="AE5" t="n">
-        <v>127321000</v>
+        <v>25328000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-285322000</v>
+        <v>11209000</v>
       </c>
       <c r="AG5" t="n">
-        <v>175316000</v>
+        <v>354027000</v>
       </c>
       <c r="AH5" t="n">
-        <v>273000</v>
+        <v>1044000</v>
       </c>
       <c r="AI5" t="n">
-        <v>103558000</v>
+        <v>121829000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>53053000</v>
+        <v>35124000</v>
       </c>
       <c r="AK5" t="n">
-        <v>53053000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>232000</v>
-      </c>
+        <v>35124000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-54139000</v>
+        <v>-653539000</v>
       </c>
     </row>
   </sheetData>
@@ -3560,192 +3560,192 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jianqiu  Yu', 'age': 60, 'title': 'Founder, Chairman &amp; CEO', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 3479958, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yufen  Zhu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 553735, 'exercisedValue': 0, 'unexercisedValue': 1703685}, {'maxAge': 1, 'name': 'Mr. Qiang  Gao', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 193460, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ngai Chi  Chan C.F.A., FCCA, FCPA', 'age': 53, 'title': 'Chief Financial Officer', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Guidi  Luo', 'age': 50, 'title': 'Risk Management Officer and Controller', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Kwan  Cheung AHKSA, CPA, FCCA', 'age': 65, 'title': 'Company Secretary', 'yearBorn': 1960, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jianqiu  Yu', 'age': 60, 'title': 'Founder, Chairman &amp; CEO', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 3477185, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yufen  Zhu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 553294, 'exercisedValue': 0, 'unexercisedValue': 1702327}, {'maxAge': 1, 'name': 'Mr. Qiang  Gao', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 193306, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ngai Chi  Chan C.F.A., FCCA, FCPA', 'age': 53, 'title': 'Chief Financial Officer', 'yearBorn': 1972, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Guidi  Luo', 'age': 50, 'title': 'Risk Management Officer and Controller', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Kwan  Cheung AHKSA, CPA, FCCA', 'age': 65, 'title': 'Company Secretary', 'yearBorn': 1960, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.441</v>
+        <v>0.499</v>
       </c>
       <c r="AD2" t="n">
         <v>514000</v>
@@ -3877,7 +3877,7 @@
         <v>514000</v>
       </c>
       <c r="AF2" t="n">
-        <v>63846</v>
+        <v>46074</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>138928275</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.27</v>
+        <v>0.305</v>
       </c>
       <c r="AP2" t="n">
         <v>1.7</v>
@@ -3919,10 +3919,10 @@
         <v>0.3916915</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.3191</v>
+        <v>0.31</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.644625</v>
+        <v>0.588525</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3960,7 +3960,7 @@
         <v>448155726</v>
       </c>
       <c r="BG2" t="n">
-        <v>-11.275109</v>
+        <v>-11.266212</v>
       </c>
       <c r="BH2" t="n">
         <v>1735603200</v>
@@ -3992,10 +3992,10 @@
         <v>-10.338</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.2051282</v>
+        <v>0.016393423</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>0.3</v>
@@ -4102,143 +4102,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CV2" t="n">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>CMRU</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>-8.823529000000001</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_256717288</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1774943968</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.278525</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.47325942</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.027515903</v>
+      </c>
+      <c r="DN2" t="n">
         <v>15</v>
       </c>
-      <c r="CW2" t="b">
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="b">
         <v>0</v>
       </c>
-      <c r="CX2" t="b">
+      <c r="DQ2" t="n">
+        <v>1392946200000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.030000001</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.305 - 0.33</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.004999995</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.016393427</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>0.305 - 1.7</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-1.3900001</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.8176471</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1.6393423</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1743426522</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1743426522</v>
+      </c>
+      <c r="ED2" t="b">
         <v>0</v>
       </c>
-      <c r="CY2" t="n">
-        <v>1392946200000</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>1774943968</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>finmb_256717288</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
+      <c r="EE2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>China Metal Resources Utilization Limited</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-8.823529000000001</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>China Metal Resources Utilization Limited</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CMRU</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.030000001</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0.305 - 0.33</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>63846</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.03999999</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.1481481</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>0.27 - 1.7</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-1.3900001</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.8176471</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-20.51282</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1743426522</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1743426522</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.009099990000000001</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.028517677</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.334625</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.51910025</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.02749419</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
       </c>
       <c r="EH2" t="inlineStr"/>
     </row>
